--- a/data/input/customers.xlsx
+++ b/data/input/customers.xlsx
@@ -1,44 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="顧客マスタ" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>顧客ID</t>
+  </si>
+  <si>
+    <t>顧客名</t>
+  </si>
+  <si>
+    <t>メール</t>
+  </si>
+  <si>
+    <t>C0001</t>
+  </si>
+  <si>
+    <t>株式会社さくら畜産</t>
+  </si>
+  <si>
+    <t>info@sakura-chikusan.jp</t>
+  </si>
+  <si>
+    <t>C0002</t>
+  </si>
+  <si>
+    <t>みどり養豚場</t>
+  </si>
+  <si>
+    <t>midori@example.jp</t>
+  </si>
+  <si>
+    <t>C0003</t>
+  </si>
+  <si>
+    <t>北海道ファーム合同会社</t>
+  </si>
+  <si>
+    <t>contact@hokkaido-farm.jp</t>
+  </si>
+  <si>
+    <t>C0004</t>
+  </si>
+  <si>
+    <t>九州アグリ協同組合</t>
+  </si>
+  <si>
+    <t>info@kyushu-agri.jp</t>
+  </si>
+  <si>
+    <t>C0005</t>
+  </si>
+  <si>
+    <t>山田畜産</t>
+  </si>
+  <si>
+    <t>yamada@example.jp</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
+        <fgColor rgb="FFE3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,81 +109,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -208,6 +203,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -242,6 +238,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -276,20 +273,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -411,128 +404,127 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>株式会社さくら畜産</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>info@sakura-chikusan.example.jp</t>
-        </is>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C0002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>みどり養豚場</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>midori@example.jp</t>
-        </is>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C0003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>北海道ファーム合同会社</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>office@hokkaido-farm.example.jp</t>
-        </is>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C0004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>九州アグリ協同組合</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>kyushu-agri@example.jp</t>
-        </is>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C0005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>山田畜産</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>yamada@example.jp</t>
-        </is>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/input/customers.xlsx
+++ b/data/input/customers.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DD351E-74D4-4259-90C0-9CB507290D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="顧客マスタ" state="visible" r:id="rId4"/>
+    <sheet name="顧客マスタ" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>顧客ID</t>
   </si>
@@ -25,62 +29,102 @@
     <t>C0001</t>
   </si>
   <si>
-    <t>株式会社さくら畜産</t>
-  </si>
-  <si>
-    <t>info@sakura-chikusan.jp</t>
-  </si>
-  <si>
     <t>C0002</t>
   </si>
   <si>
-    <t>みどり養豚場</t>
-  </si>
-  <si>
-    <t>midori@example.jp</t>
-  </si>
-  <si>
     <t>C0003</t>
   </si>
   <si>
-    <t>北海道ファーム合同会社</t>
-  </si>
-  <si>
-    <t>contact@hokkaido-farm.jp</t>
-  </si>
-  <si>
     <t>C0004</t>
   </si>
   <si>
-    <t>九州アグリ協同組合</t>
-  </si>
-  <si>
-    <t>info@kyushu-agri.jp</t>
-  </si>
-  <si>
     <t>C0005</t>
   </si>
   <si>
-    <t>山田畜産</t>
-  </si>
-  <si>
-    <t>yamada@example.jp</t>
+    <t>株式会社ヒラノ　睦沢農場</t>
+    <rPh sb="8" eb="12">
+      <t>ムツザワノウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>株式会社ヒラノ　多古農場</t>
+    <rPh sb="8" eb="10">
+      <t>タコ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ノウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>株式会社ヒラノ　大田原農場</t>
+    <rPh sb="8" eb="11">
+      <t>オオタワラ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ノウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>株式会社ヒラノ　那須農場</t>
+    <rPh sb="8" eb="10">
+      <t>ナス</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ノウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>株式会社ヒラノ　丸山農場</t>
+    <rPh sb="8" eb="10">
+      <t>マルヤマ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ノウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>info@hirano.jp</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -105,15 +149,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -449,15 +496,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,63 +515,68 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{4EFB9E5A-5333-4DA9-BA0C-6789E552D535}"/>
+    <hyperlink ref="C3:C6" r:id="rId2" display="info@hirano.jp" xr:uid="{6123D191-C8C9-4DD7-BE25-0798BFCD9080}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/input/customers.xlsx
+++ b/data/input/customers.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DD351E-74D4-4259-90C0-9CB507290D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739EB7DD-C85D-4E0D-8A7E-25E68B73C32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>顧客ID</t>
   </si>
@@ -89,6 +89,45 @@
   </si>
   <si>
     <t>info@hirano.jp</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C0006</t>
+  </si>
+  <si>
+    <t>C0007</t>
+  </si>
+  <si>
+    <t>C0008</t>
+  </si>
+  <si>
+    <t>株式会社ヒラノ　穂積農場</t>
+    <rPh sb="8" eb="10">
+      <t>ホズミ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ノウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>株式会社ヒラノ　旭ヶ丘農場</t>
+    <rPh sb="8" eb="11">
+      <t>アサヒガオカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ノウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>株式会社ヒラノ　十余三農場</t>
+    <rPh sb="8" eb="11">
+      <t>トヨミ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ノウジョウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -497,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -570,11 +609,46 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{4EFB9E5A-5333-4DA9-BA0C-6789E552D535}"/>
     <hyperlink ref="C3:C6" r:id="rId2" display="info@hirano.jp" xr:uid="{6123D191-C8C9-4DD7-BE25-0798BFCD9080}"/>
+    <hyperlink ref="C7:C8" r:id="rId3" display="info@hirano.jp" xr:uid="{B9763CD6-AB0D-4A95-86AA-44F5235801CE}"/>
+    <hyperlink ref="C9" r:id="rId4" xr:uid="{E8BA8B6F-FD62-4508-8BCF-A962EABB68EC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
